--- a/Result/profitability/5432.xlsx
+++ b/Result/profitability/5432.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4275</v>
+        <v>1.28875</v>
       </c>
       <c r="N2" t="n">
-        <v>23.615</v>
+        <v>23.8775</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.38875</v>
+        <v>1.2425</v>
       </c>
       <c r="N3" t="n">
-        <v>21.57125</v>
+        <v>22.2875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.35375</v>
+        <v>1.23125</v>
       </c>
       <c r="N4" t="n">
-        <v>19.3</v>
+        <v>19.54125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
         <v>-9.15</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.04875000000000007</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1127,7 +1127,7 @@
         <v>0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8287500000000001</v>
+        <v>-0.007499999999999996</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1250,7 +1250,7 @@
         <v>-1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.08375</v>
+        <v>-0.33875</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1375,7 +1375,7 @@
         <v>-0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.25625</v>
+        <v>-0.3925</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9798,6 +9798,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5432</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>50</v>
+      </c>
+      <c r="D75" t="n">
+        <v>37</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>144</v>
+      </c>
+      <c r="J75" t="n">
+        <v>149</v>
+      </c>
+      <c r="K75" t="n">
+        <v>149</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.29875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.0225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="X75" t="n">
+        <v>25.59259259259259</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.399999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1155283724091063</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>22.16129032258064</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.830000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1219827586206896</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
